--- a/tests/testthat/fixtures/testform.xlsx
+++ b/tests/testthat/fixtures/testform.xlsx
@@ -257,49 +257,115 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">begin repeat</t>
+          <t xml:space="preserve">geopoint</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t xml:space="preserve">plot_rpt</t>
+          <t xml:space="preserve">gps</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve">መሬቶች</t>
+          <t xml:space="preserve">ቦታ</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Plots</t>
+          <t xml:space="preserve">Location of the household</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">integer</t>
+          <t xml:space="preserve">select_multiple diseases or_other</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t xml:space="preserve">plot_size</t>
+          <t xml:space="preserve">illness</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">የመሬት መጠን</t>
+          <t xml:space="preserve">በሽታዎች</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Plot size</t>
+          <t xml:space="preserve">Illnesses reported</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">any_selected</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ማንኛውም</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Deliberate clash with the zero-fill helper</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">begin repeat</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">plot_rpt</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">መሬቶች</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Plots</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">integer</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">plot_size</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">የመሬት መጠን</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Plot size</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
         <is>
           <t xml:space="preserve">end repeat</t>
         </is>
@@ -444,6 +510,50 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">diseases</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ወባ</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Malaria</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">diseases</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ታይፎይድ</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Typhoid</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>

--- a/tests/testthat/fixtures/testform.xlsx
+++ b/tests/testthat/fixtures/testform.xlsx
@@ -147,225 +147,298 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">integer</t>
+          <t xml:space="preserve">note</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">hh_size</t>
+          <t xml:space="preserve">note_intro</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">የቤተሰብ ብዛት</t>
+          <t xml:space="preserve">መግቢያ</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Household size</t>
+          <t xml:space="preserve">Welcome to the survey</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">decimal</t>
+          <t xml:space="preserve">begin_group</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">land_area</t>
+          <t xml:space="preserve">grp_demog</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">የመሬት ስፋት</t>
+          <t xml:space="preserve">ስነ ሕዝብ</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Land area in ha (±0.1)</t>
+          <t xml:space="preserve">Demographics</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">integer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">resp_name</t>
+          <t xml:space="preserve">hh_size</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">ስም</t>
+          <t xml:space="preserve">የቤተሰብ ብዛት</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Respondent &lt;b&gt;name&lt;/b&gt;</t>
+          <t xml:space="preserve">Household size</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">select_one yn</t>
+          <t xml:space="preserve">decimal</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t xml:space="preserve">owns_land</t>
+          <t xml:space="preserve">land_area</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">መሬት አለው?</t>
+          <t xml:space="preserve">የመሬት ስፋት</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Does the household own land? Cost ($USD)</t>
+          <t xml:space="preserve">Land area in ha (±0.1)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">select_multiple crops</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">crops</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ሰብሎች</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Crops grown</t>
+          <t xml:space="preserve">end_group</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">geopoint</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t xml:space="preserve">gps</t>
+          <t xml:space="preserve">resp_name</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve">ቦታ</t>
+          <t xml:space="preserve">ስም</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Location of the household</t>
+          <t xml:space="preserve">Respondent &lt;b&gt;name&lt;/b&gt;</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">select_multiple diseases or_other</t>
+          <t xml:space="preserve">select_one yn</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t xml:space="preserve">illness</t>
+          <t xml:space="preserve">owns_land</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">በሽታዎች</t>
+          <t xml:space="preserve">መሬት አለው?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Illnesses reported</t>
+          <t xml:space="preserve">Does the household own land? Cost ($USD)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">select_multiple crops</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t xml:space="preserve">any_selected</t>
+          <t xml:space="preserve">crops</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve">ማንኛውም</t>
+          <t xml:space="preserve">ሰብሎች</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Deliberate clash with the zero-fill helper</t>
+          <t xml:space="preserve">Crops grown</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">begin repeat</t>
+          <t xml:space="preserve">geopoint</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t xml:space="preserve">plot_rpt</t>
+          <t xml:space="preserve">gps</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t xml:space="preserve">መሬቶች</t>
+          <t xml:space="preserve">ቦታ</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Plots</t>
+          <t xml:space="preserve">Location of the household</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">integer</t>
+          <t xml:space="preserve">select_multiple diseases or_other</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t xml:space="preserve">plot_size</t>
+          <t xml:space="preserve">illness</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t xml:space="preserve">የመሬት መጠን</t>
+          <t xml:space="preserve">በሽታዎች</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Plot size</t>
+          <t xml:space="preserve">Illnesses reported</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">any_selected</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ማንኛውም</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Deliberate clash with the zero-fill helper</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">begin repeat</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">plot_rpt</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">መሬቶች</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Plots</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">note</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">note_plot</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ማስታወሻ</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">About this plot</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">integer</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">plot_size</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">የመሬት መጠን</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Plot size</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
         <is>
           <t xml:space="preserve">end repeat</t>
         </is>
